--- a/data/b2_primavera/B2 Primavera 11-2025.xlsx
+++ b/data/b2_primavera/B2 Primavera 11-2025.xlsx
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1050.3</v>
+        <v>1033.81</v>
       </c>
     </row>
     <row r="3">
@@ -4743,43 +4743,43 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57769.72</v>
+        <v>57502.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45970</v>
+        <v>45968</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3886.52</v>
+        <v>1029.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>14000</v>
+        <v>3666.43</v>
       </c>
     </row>
     <row r="6">
@@ -4788,34 +4788,34 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3600</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>45973</v>
+        <v>45971</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1955.64</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="8">
@@ -4824,34 +4824,34 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1151.93</v>
+        <v>2847.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>45974</v>
+        <v>45973</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>701.42</v>
+        <v>1149.19</v>
       </c>
     </row>
     <row r="10">
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9239.209999999999</v>
+        <v>9391.9</v>
       </c>
     </row>
     <row r="11">
@@ -4887,7 +4887,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1597.97</v>
+        <v>1743.03</v>
       </c>
     </row>
     <row r="12">
@@ -4896,21 +4896,21 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1104.97</v>
+        <v>4108.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>45977</v>
+        <v>45979</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -4919,83 +4919,83 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1096.63</v>
+        <v>1261.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45977</v>
+        <v>45981</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3920.54</v>
+        <v>20657.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>45981</v>
+        <v>45984</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>20064.34</v>
+        <v>1328.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45982</v>
+        <v>45984</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2917.55</v>
+        <v>3612.76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3941.37</v>
+        <v>2447.26</v>
       </c>
     </row>
     <row r="18">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3557.33</v>
+        <v>3825.49</v>
       </c>
     </row>
   </sheetData>
